--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132763491</v>
+        <v>132763492</v>
       </c>
       <c r="B2" t="n">
-        <v>4775</v>
+        <v>96783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>300 m S Dalsberg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577878</v>
+        <v>577873</v>
       </c>
       <c r="R2" t="n">
-        <v>6315846</v>
+        <v>6315967</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -780,7 +775,7 @@
         <v>132763493</v>
       </c>
       <c r="B3" t="n">
-        <v>78691</v>
+        <v>78731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132763492</v>
+        <v>132763491</v>
       </c>
       <c r="B4" t="n">
-        <v>96718</v>
+        <v>4776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,37 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>300 m S Dalsberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577873</v>
+        <v>577878</v>
       </c>
       <c r="R4" t="n">
-        <v>6315967</v>
+        <v>6315846</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,6 +968,108 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132763490</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>300 m S Dalsberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>577850</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6315926</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132763492</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132763493</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132763491</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,8 +1090,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132763490</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,48 +782,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132763493</v>
+        <v>135760703</v>
       </c>
       <c r="B3" t="n">
-        <v>78731</v>
+        <v>92069</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6443</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>300 m S Dalsberg, Sm</t>
+          <t>Dalsberg, Dalsberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577873</v>
+        <v>577891</v>
       </c>
       <c r="R3" t="n">
-        <v>6315967</v>
+        <v>6315952</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +876,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132763493</t>
+          <t>https://artportalen.se/Sighting/135760703</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132763491</v>
+        <v>132763493</v>
       </c>
       <c r="B4" t="n">
-        <v>4776</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,39 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>6443</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>300 m S Dalsberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577878</v>
+        <v>577873</v>
       </c>
       <c r="R4" t="n">
-        <v>6315846</v>
+        <v>6315967</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,16 +989,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132763491</t>
+          <t>https://artportalen.se/Sighting/132763493</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132763490</v>
+        <v>135760832</v>
       </c>
       <c r="B5" t="n">
-        <v>5181</v>
+        <v>57977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,39 +1006,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>300 m S Dalsberg, Sm</t>
+          <t>Dalsberg, Dalsberg, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577850</v>
+        <v>577891</v>
       </c>
       <c r="R5" t="n">
-        <v>6315926</v>
+        <v>6315952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,12 +1065,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,18 +1085,683 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135760832</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135761187</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dalsberg, Dalsberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>577859</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6315875</v>
+      </c>
+      <c r="S6" t="n">
+        <v>7</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135761187</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132763491</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>300 m S Dalsberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>577878</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6315846</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132763491</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132763490</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>300 m S Dalsberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>577850</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6315926</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/132763490</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135762631</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dalsberg, Dalsberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577874</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6315797</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135762631</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135761529</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dalsberg, Dalsberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>577859</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6315875</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135761529</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135762469</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sjökärren, Sjökärren, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>577881</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6315839</v>
+      </c>
+      <c r="S11" t="n">
+        <v>7</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135762469</t>
         </is>
       </c>
     </row>
@@ -1102,6 +1771,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135760703</v>
       </c>
       <c r="B3" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>135761529</v>
       </c>
       <c r="B10" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>135762469</v>
       </c>
       <c r="B11" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135760703</v>
       </c>
       <c r="B3" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>135760832</v>
       </c>
       <c r="B5" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>135761187</v>
       </c>
       <c r="B6" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>135762631</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>8452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>135761529</v>
       </c>
       <c r="B10" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>135762469</v>
       </c>
       <c r="B11" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135760703</v>
       </c>
       <c r="B3" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>135761529</v>
       </c>
       <c r="B10" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>135762469</v>
       </c>
       <c r="B11" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135760703</v>
       </c>
       <c r="B3" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>135761529</v>
       </c>
       <c r="B10" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>135762469</v>
       </c>
       <c r="B11" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135760703</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>135760832</v>
       </c>
       <c r="B5" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>135761187</v>
       </c>
       <c r="B6" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>135761529</v>
       </c>
       <c r="B10" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>135762469</v>
       </c>
       <c r="B11" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135760703</v>
       </c>
       <c r="B3" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>135760832</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>135761187</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>135761529</v>
       </c>
       <c r="B10" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>135762469</v>
       </c>
       <c r="B11" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135760703</v>
       </c>
       <c r="B3" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>135760832</v>
       </c>
       <c r="B5" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>135761187</v>
       </c>
       <c r="B6" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>135761529</v>
       </c>
       <c r="B10" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>135762469</v>
       </c>
       <c r="B11" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135760703</v>
       </c>
       <c r="B3" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>135761529</v>
       </c>
       <c r="B10" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>135762469</v>
       </c>
       <c r="B11" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135760703</v>
       </c>
       <c r="B3" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>135760832</v>
       </c>
       <c r="B5" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>135761187</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>135761529</v>
       </c>
       <c r="B10" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>135762469</v>
       </c>
       <c r="B11" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,57 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135760703</v>
+        <v>136488293</v>
       </c>
       <c r="B3" t="n">
-        <v>92108</v>
+        <v>96926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dalsberg, Dalsberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577891</v>
+        <v>577864</v>
       </c>
       <c r="R3" t="n">
-        <v>6315952</v>
+        <v>6315873</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,54 +878,63 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135760703</t>
+          <t>https://artportalen.se/Sighting/136488293</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132763493</v>
+        <v>135760703</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>92108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6443</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>300 m S Dalsberg, Sm</t>
+          <t>Dalsberg, Dalsberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577873</v>
+        <v>577891</v>
       </c>
       <c r="R4" t="n">
-        <v>6315967</v>
+        <v>6315952</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -958,12 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,27 +978,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132763493</t>
+          <t>https://artportalen.se/Sighting/135760703</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135760832</v>
+        <v>132763493</v>
       </c>
       <c r="B5" t="n">
-        <v>57990</v>
+        <v>78731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,39 +1006,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6443</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dalsberg, Dalsberg, Sm</t>
+          <t>300 m S Dalsberg, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577891</v>
+        <v>577873</v>
       </c>
       <c r="R5" t="n">
-        <v>6315952</v>
+        <v>6315967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,12 +1060,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,24 +1080,24 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135760832</t>
+          <t>https://artportalen.se/Sighting/132763493</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135761187</v>
+        <v>135760832</v>
       </c>
       <c r="B6" t="n">
         <v>57990</v>
@@ -1142,13 +1137,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577859</v>
+        <v>577891</v>
       </c>
       <c r="R6" t="n">
-        <v>6315875</v>
+        <v>6315952</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,16 +1198,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135761187</t>
+          <t>https://artportalen.se/Sighting/135760832</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132763491</v>
+        <v>135761187</v>
       </c>
       <c r="B7" t="n">
-        <v>4776</v>
+        <v>57990</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,42 +1215,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>300 m S Dalsberg, Sm</t>
+          <t>Dalsberg, Dalsberg, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577878</v>
+        <v>577859</v>
       </c>
       <c r="R7" t="n">
-        <v>6315846</v>
+        <v>6315875</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,27 +1294,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132763491</t>
+          <t>https://artportalen.se/Sighting/135761187</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132763490</v>
+        <v>132763491</v>
       </c>
       <c r="B8" t="n">
-        <v>5181</v>
+        <v>4776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577850</v>
+        <v>577878</v>
       </c>
       <c r="R8" t="n">
-        <v>6315926</v>
+        <v>6315846</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,16 +1412,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132763490</t>
+          <t>https://artportalen.se/Sighting/132763491</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135762631</v>
+        <v>132763490</v>
       </c>
       <c r="B9" t="n">
-        <v>8452</v>
+        <v>5181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,34 +1429,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dalsberg, Dalsberg, Sm</t>
+          <t>300 m S Dalsberg, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577874</v>
+        <v>577850</v>
       </c>
       <c r="R9" t="n">
-        <v>6315797</v>
+        <v>6315926</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,79 +1508,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135762631</t>
+          <t>https://artportalen.se/Sighting/132763490</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135761529</v>
+        <v>135762631</v>
       </c>
       <c r="B10" t="n">
-        <v>99327</v>
+        <v>8452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dalsberg, Dalsberg, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577859</v>
+        <v>577874</v>
       </c>
       <c r="R10" t="n">
-        <v>6315875</v>
+        <v>6315797</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1635,68 +1621,59 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135761529</t>
+          <t>https://artportalen.se/Sighting/135762631</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135762469</v>
+        <v>136488001</v>
       </c>
       <c r="B11" t="n">
-        <v>99327</v>
+        <v>8452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sjökärren, Sjökärren, Sm</t>
+          <t>Dalsberg, Dalsberg, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577881</v>
+        <v>577899</v>
       </c>
       <c r="R11" t="n">
-        <v>6315839</v>
+        <v>6315834</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1720,22 +1697,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,16 +1717,258 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian  Norrby</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136488001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135761529</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dalsberg, Dalsberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>577859</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6315875</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135761529</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135762469</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sjökärren, Sjökärren, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>577881</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6315839</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135762469</t>
         </is>
@@ -1777,6 +1986,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36372-2023 artfynd.xlsx
+++ b/artfynd/A 36372-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136488293</v>
       </c>
       <c r="B3" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
